--- a/Deterministic/Model Files/Segment Test/data/Starting_point.xlsx
+++ b/Deterministic/Model Files/Segment Test/data/Starting_point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Deterministic/Model Files/Segment Test/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{FA3337A2-F403-407B-92A1-0BBD98A29972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98964434-48BB-4FCC-96EC-352152809D98}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{FA3337A2-F403-407B-92A1-0BBD98A29972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E683AC85-8F81-4588-B76C-A733B10B44FB}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -293,10 +293,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1274,7 +1270,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="10">
-        <v>9876337950899990</v>
+        <v>987633795</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
